--- a/astro-site/public/dl/kit-escandallos/09-control-mermas.xlsx
+++ b/astro-site/public/dl/kit-escandallos/09-control-mermas.xlsx
@@ -1,16 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Mermas Semanal" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mermas Semanal" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Mermas Semanal'!$4:$4</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -18,9 +20,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
-    <numFmt formatCode="#,##0.00 €" numFmtId="164"/>
-    <numFmt formatCode="0.0%" numFmtId="165"/>
-    <numFmt formatCode="+0.0%;-0.0%" numFmtId="166"/>
+    <numFmt numFmtId="164" formatCode="#,##0.00 €"/>
+    <numFmt numFmtId="165" formatCode="0.0%"/>
+    <numFmt numFmtId="166" formatCode="+0.0%;-0.0%"/>
   </numFmts>
   <fonts count="10">
     <font>
@@ -144,59 +146,59 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="23">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="0" fillId="0" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="0" fillId="0" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="0" fillId="0" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="0" fillId="0" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="1" fillId="2" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="3" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="4" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="4" fontId="5" numFmtId="9" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="0" numFmtId="164" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="9" numFmtId="165" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="9" numFmtId="166" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="5" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="5" fontId="5" numFmtId="9" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="6" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="1" fillId="6" fontId="4" numFmtId="164" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="1" fillId="6" fontId="4" numFmtId="165" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="4" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" hidden="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium9"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -556,15 +558,16 @@
   <sheetPr>
     <tabColor rgb="00FFD700"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:B17"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="3"/>
-    <col customWidth="1" max="2" min="2" width="80"/>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="80" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -586,6 +589,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="B6" s="4" t="inlineStr">
         <is>
@@ -648,10 +652,19 @@
         </is>
       </c>
     </row>
+    <row r="16"/>
     <row r="17">
       <c r="B17" s="8" t="inlineStr">
         <is>
           <t>© 2026 AI Chef Pro · Todos los derechos reservados</t>
+        </is>
+      </c>
+    </row>
+    <row r="18"/>
+    <row r="19">
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-escandallos · info@aichef.pro</t>
         </is>
       </c>
     </row>
@@ -659,7 +672,16 @@
   <mergeCells count="1">
     <mergeCell ref="B2"/>
   </mergeCells>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -668,19 +690,19 @@
   <sheetPr>
     <tabColor rgb="00FFD700"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:H21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="22"/>
-    <col customWidth="1" max="2" min="2" width="14"/>
-    <col customWidth="1" max="3" min="3" width="16"/>
-    <col customWidth="1" max="4" min="4" width="16"/>
-    <col customWidth="1" max="5" min="5" width="14"/>
-    <col customWidth="1" max="6" min="6" width="14"/>
-    <col customWidth="1" max="7" min="7" width="14"/>
-    <col customWidth="1" max="8" min="8" width="14"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -698,6 +720,7 @@
       </c>
       <c r="B2" s="10" t="n"/>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="11" t="inlineStr">
         <is>
@@ -1148,11 +1171,11 @@
       </c>
       <c r="C21" s="21">
         <f>SUM(C5:C20)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="D21" s="21">
         <f>SUM(D5:D20)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E21" s="22">
         <f>IF(C21=0,"",D21/C21)</f>
@@ -1163,6 +1186,15 @@
   <mergeCells count="1">
     <mergeCell ref="A1:H1"/>
   </mergeCells>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
--- a/astro-site/public/dl/kit-escandallos/09-control-mermas.xlsx
+++ b/astro-site/public/dl/kit-escandallos/09-control-mermas.xlsx
@@ -9,9 +9,12 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mermas Semanal" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evolución" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Mermas Semanal'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Mermas Semanal'!$A$1:$J$24</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Evolución'!$A$1:$E$36</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -19,12 +22,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="#,##0.00 €"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
     <numFmt numFmtId="166" formatCode="+0.0%;-0.0%"/>
+    <numFmt numFmtId="167" formatCode="dd/mm/yyyy"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="16">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -83,8 +87,30 @@
       <color rgb="00333333"/>
       <sz val="11"/>
     </font>
+    <font/>
+    <font>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00606060"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="12">
     <fill>
       <patternFill/>
     </fill>
@@ -121,6 +147,31 @@
         <bgColor rgb="00FFD700"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8F5E9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002D2D2D"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5F5F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFD700"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -148,7 +199,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -194,10 +245,113 @@
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="4" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="13" fillId="7" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="13" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="13" fillId="7" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="7" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="13" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="13" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="13" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="12" fillId="11" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="12" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="12" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="13" fillId="7" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="13" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="13" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="13" fillId="7" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="165" fontId="13" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
+  <dxfs count="3">
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="009C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FFC7CE"/>
+          <bgColor rgb="00FFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="00006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00C6EFCE"/>
+          <bgColor rgb="00C6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="00FFFFFF"/>
+      </font>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -268,6 +422,157 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="2"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Desperdicio semanal vs objetivo</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Evolución'!D5</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <strRef>
+              <f>'Evolución'!$A$6:$A$17</f>
+            </strRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Evolución'!$D$6:$D$17</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Evolución'!E5</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <strRef>
+              <f>'Evolución'!$A$6:$A$17</f>
+            </strRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Evolución'!$E$6:$E$17</f>
+            </numRef>
+          </val>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="b"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <numFmt formatCode="0.0%" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>18</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="6480000" cy="3240000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -560,7 +865,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:B43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -591,80 +896,196 @@
     </row>
     <row r="5"/>
     <row r="6">
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>Cómo usar esta plantilla</t>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>▸ Esta plantilla mide el DESPERDICIO: los euros que se tiran (caducidad, mal estado, sobreproducción, porcionado) sobre los euros que se compran.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="5" t="inlineStr"/>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>▸ NO mide la merma de despiece y limpieza. Esa va en las plantillas de escandallo (hoja «Mermas») y ya está cobrada dentro del precio del plato: registrarla otra vez aquí sería contarla dos veces.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>▸ Registra las mermas reales de tu establecimiento semanalmente</t>
-        </is>
-      </c>
+      <c r="B8" s="6" t="n"/>
     </row>
     <row r="9">
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>▸ Compara con la merma estándar de la industria</t>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Cómo se rellena</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>▸ Identifica categorías donde pierdes más de lo normal</t>
-        </is>
-      </c>
+      <c r="B10" s="6" t="n"/>
     </row>
     <row r="11">
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>▸ La columna 'Diferencia' te muestra si estás por encima o por debajo</t>
+          <t>▸ Pestaña 'Mermas Semanal': escribe la fecha del lunes y, por categoría, la COMPRA de la semana y los EUROS desperdiciados.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>▸ Rojo = merma real superior al estándar (alerta)</t>
+          <t>▸ El porcentaje, la diferencia en puntos y el estado salen solos.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>▸ Verde = merma real igual o inferior al estándar (bien)</t>
+          <t>▸ Sólo se escriben las celdas VERDES. El resto son fórmulas.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="5" t="inlineStr"/>
+      <c r="B14" s="5" t="n"/>
     </row>
     <row r="15">
-      <c r="B15" s="7" t="inlineStr">
-        <is>
-          <t>— Kit de Escandallos Pro · AI Chef Pro · aichef.pro</t>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>El semáforo</t>
         </is>
       </c>
     </row>
     <row r="16"/>
     <row r="17">
-      <c r="B17" s="8" t="inlineStr">
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>▸ Estado en VERDE («OK»): el desperdicio está en el objetivo o por debajo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>▸ Estado en ROJO («ALERTA»): te estás pasando. Empieza por ahí.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>▸ La columna «Desperdicio real (%)» lleva además una escala de color: de un vistazo se ve qué categoría se sale de la fila.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20"/>
+    <row r="21">
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>Los objetivos (mín. / típico / máx.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22"/>
+    <row r="23">
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>▸ Secos y congelados 2-3 % · carne y pescado 3-5 % · verdura y fruta 5-8 % · bebidas 1-2 % · pan y bollería 5-10 %.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>▸ El «objetivo típico» es la celda verde y es el que dispara la alerta: bájalo cuando tu casa mejore.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>▸ Mínimo y máximo son la horquilla del sector: sirven para saber si tu número es normal, bueno o malo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26"/>
+    <row r="27">
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>Pestaña «Evolución»</t>
+        </is>
+      </c>
+    </row>
+    <row r="28"/>
+    <row r="29">
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>▸ Doce semanas. La primera fila («Semana en curso») está ENLAZADA al TOTAL de «Mermas Semanal»: se mueve sola mientras rellenas la semana.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>▸ Cada lunes, ANTES de vaciar el registro semanal, copia su total en la fila de la semana que cierras y pega VALORES, no fórmulas. La primera vez pegarás encima del enlace, y así debe ser: si lo dejas vivo, la semana 1 pasará a enseñar los datos de la semana 2 y perderás el histórico.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>▸ El gráfico compara tu desperdicio con el objetivo global semana a semana: la tendencia es lo que decide, no la foto de un lunes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>▸ Las semanas todavía sin rellenar devuelven #N/A a propósito: es el único valor que el gráfico SALTA. Con una celda vacía o un texto, Excel dibujaría un cero y parecería que tu desperdicio se desplomó.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33"/>
+    <row r="34">
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>Protección de la hoja</t>
+        </is>
+      </c>
+    </row>
+    <row r="35"/>
+    <row r="36">
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t>▸ Las hojas están protegidas SIN contraseña para que no borres una fórmula sin querer: sólo se escriben las celdas verdes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>▸ Para tocar cualquier otra cosa: Revisar → Desproteger hoja. No pide contraseña.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38"/>
+    <row r="39">
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t>— Kit de Escandallos Pro · AI Chef Pro · aichef.pro</t>
+        </is>
+      </c>
+    </row>
+    <row r="40"/>
+    <row r="41">
+      <c r="B41" s="6" t="inlineStr">
         <is>
           <t>© 2026 AI Chef Pro · Todos los derechos reservados</t>
         </is>
       </c>
     </row>
-    <row r="18"/>
-    <row r="19">
-      <c r="B19" s="8" t="inlineStr">
-        <is>
-          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-escandallos · info@aichef.pro</t>
+    <row r="42"/>
+    <row r="43">
+      <c r="B43" s="6" t="inlineStr">
+        <is>
+          <t>Versión 2.0 · agosto 2026 · aichef.pro/kit-escandallos · info@aichef.pro</t>
         </is>
       </c>
     </row>
@@ -692,500 +1113,702 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:J24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="30" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="9" t="inlineStr">
-        <is>
-          <t>Control de Mermas — Registro Semanal</t>
+      <c r="A1" s="23" t="inlineStr">
+        <is>
+          <t>Control de Mermas — Desperdicio semanal sobre compra</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="24" t="inlineStr">
         <is>
           <t>Semana del:</t>
         </is>
       </c>
-      <c r="B2" s="10" t="n"/>
-    </row>
-    <row r="3"/>
-    <row r="4">
-      <c r="A4" s="11" t="inlineStr">
+      <c r="B2" s="25" t="n"/>
+      <c r="C2" s="26" t="n"/>
+      <c r="D2" s="26" t="n"/>
+      <c r="E2" s="26" t="n"/>
+      <c r="F2" s="26" t="n"/>
+      <c r="G2" s="26" t="n"/>
+      <c r="H2" s="26" t="n"/>
+      <c r="I2" s="26" t="n"/>
+      <c r="J2" s="26" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="26" t="n"/>
+      <c r="B3" s="26" t="n"/>
+      <c r="C3" s="26" t="n"/>
+      <c r="D3" s="26" t="n"/>
+      <c r="E3" s="26" t="n"/>
+      <c r="F3" s="26" t="n"/>
+      <c r="G3" s="26" t="n"/>
+      <c r="H3" s="26" t="n"/>
+      <c r="I3" s="26" t="n"/>
+      <c r="J3" s="26" t="n"/>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="27" t="inlineStr">
         <is>
           <t>Categoría</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
-        <is>
-          <t>Merma Estándar</t>
-        </is>
-      </c>
-      <c r="C4" s="11" t="inlineStr">
-        <is>
-          <t>Compra Total (€)</t>
-        </is>
-      </c>
-      <c r="D4" s="11" t="inlineStr">
-        <is>
-          <t>Merma Real (€)</t>
-        </is>
-      </c>
-      <c r="E4" s="11" t="inlineStr">
-        <is>
-          <t>Merma Real (%)</t>
-        </is>
-      </c>
-      <c r="F4" s="11" t="inlineStr">
-        <is>
-          <t>Diferencia (%)</t>
-        </is>
-      </c>
-      <c r="G4" s="11" t="inlineStr">
+      <c r="B4" s="27" t="inlineStr">
+        <is>
+          <t>Objetivo mín.</t>
+        </is>
+      </c>
+      <c r="C4" s="27" t="inlineStr">
+        <is>
+          <t>Objetivo típico</t>
+        </is>
+      </c>
+      <c r="D4" s="27" t="inlineStr">
+        <is>
+          <t>Objetivo máx.</t>
+        </is>
+      </c>
+      <c r="E4" s="27" t="inlineStr">
+        <is>
+          <t>Compra total (€)</t>
+        </is>
+      </c>
+      <c r="F4" s="27" t="inlineStr">
+        <is>
+          <t>Desperdicio real (€)</t>
+        </is>
+      </c>
+      <c r="G4" s="27" t="inlineStr">
+        <is>
+          <t>Desperdicio real (%)</t>
+        </is>
+      </c>
+      <c r="H4" s="27" t="inlineStr">
+        <is>
+          <t>Diferencia (p.p.)</t>
+        </is>
+      </c>
+      <c r="I4" s="28" t="inlineStr">
         <is>
           <t>Estado</t>
         </is>
       </c>
-      <c r="H4" s="11" t="inlineStr">
+      <c r="J4" s="28" t="inlineStr">
         <is>
           <t>Notas</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="12" t="inlineStr">
+      <c r="A5" s="29" t="inlineStr">
         <is>
           <t>Carne roja</t>
         </is>
       </c>
-      <c r="B5" s="13" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="C5" s="14" t="n"/>
-      <c r="D5" s="14" t="n"/>
-      <c r="E5" s="15">
-        <f>IF(C5=0,"",D5/C5)</f>
-        <v/>
-      </c>
-      <c r="F5" s="16">
-        <f>IF(E5="","",E5-B5)</f>
-        <v/>
-      </c>
-      <c r="G5" s="17">
-        <f>IF(E5="","",IF(E5&lt;=B5,"OK","ALERTA"))</f>
-        <v/>
-      </c>
-      <c r="H5" s="10" t="n"/>
+      <c r="B5" s="30" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="C5" s="31" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="D5" s="30" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E5" s="32" t="n">
+        <v>1850</v>
+      </c>
+      <c r="F5" s="32" t="n">
+        <v>74</v>
+      </c>
+      <c r="G5" s="30">
+        <f>IFERROR(IF(E5=0,"",F5/E5),"")</f>
+        <v>0.04</v>
+      </c>
+      <c r="H5" s="33">
+        <f>IFERROR(IF(G5="","",G5-C5),"")</f>
+        <v>0.0</v>
+      </c>
+      <c r="I5" s="34" t="str">
+        <f>IFERROR(IF(G5="","",IF(G5&lt;=C5,"OK","ALERTA")),"")</f>
+        <v>OK</v>
+      </c>
+      <c r="J5" s="35" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="18" t="inlineStr">
+      <c r="A6" s="36" t="inlineStr">
         <is>
           <t>Aves</t>
         </is>
       </c>
-      <c r="B6" s="19" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="C6" s="14" t="n"/>
-      <c r="D6" s="14" t="n"/>
-      <c r="E6" s="15">
-        <f>IF(C6=0,"",D6/C6)</f>
-        <v/>
-      </c>
-      <c r="F6" s="16">
-        <f>IF(E6="","",E6-B6)</f>
-        <v/>
-      </c>
-      <c r="G6" s="17">
-        <f>IF(E6="","",IF(E6&lt;=B6,"OK","ALERTA"))</f>
-        <v/>
-      </c>
-      <c r="H6" s="10" t="n"/>
+      <c r="B6" s="37" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="C6" s="31" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="D6" s="37" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E6" s="32" t="n"/>
+      <c r="F6" s="32" t="n"/>
+      <c r="G6" s="37">
+        <f>IFERROR(IF(E6=0,"",F6/E6),"")</f>
+        <v/>
+      </c>
+      <c r="H6" s="38">
+        <f>IFERROR(IF(G6="","",G6-C6),"")</f>
+        <v/>
+      </c>
+      <c r="I6" s="39">
+        <f>IFERROR(IF(G6="","",IF(G6&lt;=C6,"OK","ALERTA")),"")</f>
+        <v/>
+      </c>
+      <c r="J6" s="35" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="12" t="inlineStr">
+      <c r="A7" s="29" t="inlineStr">
         <is>
           <t>Pescado</t>
         </is>
       </c>
-      <c r="B7" s="13" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="C7" s="14" t="n"/>
-      <c r="D7" s="14" t="n"/>
-      <c r="E7" s="15">
-        <f>IF(C7=0,"",D7/C7)</f>
-        <v/>
-      </c>
-      <c r="F7" s="16">
-        <f>IF(E7="","",E7-B7)</f>
-        <v/>
-      </c>
-      <c r="G7" s="17">
-        <f>IF(E7="","",IF(E7&lt;=B7,"OK","ALERTA"))</f>
-        <v/>
-      </c>
-      <c r="H7" s="10" t="n"/>
+      <c r="B7" s="30" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="C7" s="31" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="D7" s="30" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E7" s="32" t="n">
+        <v>1240</v>
+      </c>
+      <c r="F7" s="32" t="n">
+        <v>87</v>
+      </c>
+      <c r="G7" s="30">
+        <f>IFERROR(IF(E7=0,"",F7/E7),"")</f>
+        <v>0.07016129032258064</v>
+      </c>
+      <c r="H7" s="33">
+        <f>IFERROR(IF(G7="","",G7-C7),"")</f>
+        <v>0.030161290322580643</v>
+      </c>
+      <c r="I7" s="34" t="str">
+        <f>IFERROR(IF(G7="","",IF(G7&lt;=C7,"OK","ALERTA")),"")</f>
+        <v>ALERTA</v>
+      </c>
+      <c r="J7" s="35" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="18" t="inlineStr">
+      <c r="A8" s="36" t="inlineStr">
         <is>
           <t>Marisco</t>
         </is>
       </c>
-      <c r="B8" s="19" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="C8" s="14" t="n"/>
-      <c r="D8" s="14" t="n"/>
-      <c r="E8" s="15">
-        <f>IF(C8=0,"",D8/C8)</f>
-        <v/>
-      </c>
-      <c r="F8" s="16">
-        <f>IF(E8="","",E8-B8)</f>
-        <v/>
-      </c>
-      <c r="G8" s="17">
-        <f>IF(E8="","",IF(E8&lt;=B8,"OK","ALERTA"))</f>
-        <v/>
-      </c>
-      <c r="H8" s="10" t="n"/>
+      <c r="B8" s="37" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="C8" s="31" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D8" s="37" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="E8" s="32" t="n"/>
+      <c r="F8" s="32" t="n"/>
+      <c r="G8" s="37">
+        <f>IFERROR(IF(E8=0,"",F8/E8),"")</f>
+        <v/>
+      </c>
+      <c r="H8" s="38">
+        <f>IFERROR(IF(G8="","",G8-C8),"")</f>
+        <v/>
+      </c>
+      <c r="I8" s="39">
+        <f>IFERROR(IF(G8="","",IF(G8&lt;=C8,"OK","ALERTA")),"")</f>
+        <v/>
+      </c>
+      <c r="J8" s="35" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="12" t="inlineStr">
+      <c r="A9" s="29" t="inlineStr">
         <is>
           <t>Verdura hoja</t>
         </is>
       </c>
-      <c r="B9" s="13" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="C9" s="14" t="n"/>
-      <c r="D9" s="14" t="n"/>
-      <c r="E9" s="15">
-        <f>IF(C9=0,"",D9/C9)</f>
-        <v/>
-      </c>
-      <c r="F9" s="16">
-        <f>IF(E9="","",E9-B9)</f>
-        <v/>
-      </c>
-      <c r="G9" s="17">
-        <f>IF(E9="","",IF(E9&lt;=B9,"OK","ALERTA"))</f>
-        <v/>
-      </c>
-      <c r="H9" s="10" t="n"/>
+      <c r="B9" s="30" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="C9" s="31" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="D9" s="30" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="E9" s="32" t="n">
+        <v>620</v>
+      </c>
+      <c r="F9" s="32" t="n">
+        <v>38</v>
+      </c>
+      <c r="G9" s="30">
+        <f>IFERROR(IF(E9=0,"",F9/E9),"")</f>
+        <v>0.06129032258064516</v>
+      </c>
+      <c r="H9" s="33">
+        <f>IFERROR(IF(G9="","",G9-C9),"")</f>
+        <v>-0.008709677419354848</v>
+      </c>
+      <c r="I9" s="34" t="str">
+        <f>IFERROR(IF(G9="","",IF(G9&lt;=C9,"OK","ALERTA")),"")</f>
+        <v>OK</v>
+      </c>
+      <c r="J9" s="35" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="18" t="inlineStr">
+      <c r="A10" s="36" t="inlineStr">
         <is>
           <t>Verdura raíz</t>
         </is>
       </c>
-      <c r="B10" s="19" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="C10" s="14" t="n"/>
-      <c r="D10" s="14" t="n"/>
-      <c r="E10" s="15">
-        <f>IF(C10=0,"",D10/C10)</f>
-        <v/>
-      </c>
-      <c r="F10" s="16">
-        <f>IF(E10="","",E10-B10)</f>
-        <v/>
-      </c>
-      <c r="G10" s="17">
-        <f>IF(E10="","",IF(E10&lt;=B10,"OK","ALERTA"))</f>
-        <v/>
-      </c>
-      <c r="H10" s="10" t="n"/>
+      <c r="B10" s="37" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="C10" s="31" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="D10" s="37" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="E10" s="32" t="n"/>
+      <c r="F10" s="32" t="n"/>
+      <c r="G10" s="37">
+        <f>IFERROR(IF(E10=0,"",F10/E10),"")</f>
+        <v/>
+      </c>
+      <c r="H10" s="38">
+        <f>IFERROR(IF(G10="","",G10-C10),"")</f>
+        <v/>
+      </c>
+      <c r="I10" s="39">
+        <f>IFERROR(IF(G10="","",IF(G10&lt;=C10,"OK","ALERTA")),"")</f>
+        <v/>
+      </c>
+      <c r="J10" s="35" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="12" t="inlineStr">
+      <c r="A11" s="29" t="inlineStr">
         <is>
           <t>Fruta</t>
         </is>
       </c>
-      <c r="B11" s="13" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="C11" s="14" t="n"/>
-      <c r="D11" s="14" t="n"/>
-      <c r="E11" s="15">
-        <f>IF(C11=0,"",D11/C11)</f>
-        <v/>
-      </c>
-      <c r="F11" s="16">
-        <f>IF(E11="","",E11-B11)</f>
-        <v/>
-      </c>
-      <c r="G11" s="17">
-        <f>IF(E11="","",IF(E11&lt;=B11,"OK","ALERTA"))</f>
-        <v/>
-      </c>
-      <c r="H11" s="10" t="n"/>
+      <c r="B11" s="30" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="C11" s="31" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="D11" s="30" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="E11" s="32" t="n"/>
+      <c r="F11" s="32" t="n"/>
+      <c r="G11" s="30">
+        <f>IFERROR(IF(E11=0,"",F11/E11),"")</f>
+        <v/>
+      </c>
+      <c r="H11" s="33">
+        <f>IFERROR(IF(G11="","",G11-C11),"")</f>
+        <v/>
+      </c>
+      <c r="I11" s="34">
+        <f>IFERROR(IF(G11="","",IF(G11&lt;=C11,"OK","ALERTA")),"")</f>
+        <v/>
+      </c>
+      <c r="J11" s="35" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="18" t="inlineStr">
+      <c r="A12" s="36" t="inlineStr">
         <is>
           <t>Lácteos</t>
         </is>
       </c>
-      <c r="B12" s="19" t="n">
+      <c r="B12" s="37" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="C12" s="31" t="n">
         <v>0.03</v>
       </c>
-      <c r="C12" s="14" t="n"/>
-      <c r="D12" s="14" t="n"/>
-      <c r="E12" s="15">
-        <f>IF(C12=0,"",D12/C12)</f>
-        <v/>
-      </c>
-      <c r="F12" s="16">
-        <f>IF(E12="","",E12-B12)</f>
-        <v/>
-      </c>
-      <c r="G12" s="17">
-        <f>IF(E12="","",IF(E12&lt;=B12,"OK","ALERTA"))</f>
-        <v/>
-      </c>
-      <c r="H12" s="10" t="n"/>
+      <c r="D12" s="37" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="E12" s="32" t="n">
+        <v>480</v>
+      </c>
+      <c r="F12" s="32" t="n">
+        <v>12</v>
+      </c>
+      <c r="G12" s="37">
+        <f>IFERROR(IF(E12=0,"",F12/E12),"")</f>
+        <v>0.025</v>
+      </c>
+      <c r="H12" s="38">
+        <f>IFERROR(IF(G12="","",G12-C12),"")</f>
+        <v>-0.0049999999999999975</v>
+      </c>
+      <c r="I12" s="39" t="str">
+        <f>IFERROR(IF(G12="","",IF(G12&lt;=C12,"OK","ALERTA")),"")</f>
+        <v>OK</v>
+      </c>
+      <c r="J12" s="35" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="12" t="inlineStr">
+      <c r="A13" s="29" t="inlineStr">
         <is>
           <t>Secos/granos</t>
         </is>
       </c>
-      <c r="B13" s="13" t="n">
+      <c r="B13" s="30" t="n">
         <v>0.02</v>
       </c>
-      <c r="C13" s="14" t="n"/>
-      <c r="D13" s="14" t="n"/>
-      <c r="E13" s="15">
-        <f>IF(C13=0,"",D13/C13)</f>
-        <v/>
-      </c>
-      <c r="F13" s="16">
-        <f>IF(E13="","",E13-B13)</f>
-        <v/>
-      </c>
-      <c r="G13" s="17">
-        <f>IF(E13="","",IF(E13&lt;=B13,"OK","ALERTA"))</f>
-        <v/>
-      </c>
-      <c r="H13" s="10" t="n"/>
+      <c r="C13" s="31" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="D13" s="30" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="E13" s="32" t="n"/>
+      <c r="F13" s="32" t="n"/>
+      <c r="G13" s="30">
+        <f>IFERROR(IF(E13=0,"",F13/E13),"")</f>
+        <v/>
+      </c>
+      <c r="H13" s="33">
+        <f>IFERROR(IF(G13="","",G13-C13),"")</f>
+        <v/>
+      </c>
+      <c r="I13" s="34">
+        <f>IFERROR(IF(G13="","",IF(G13&lt;=C13,"OK","ALERTA")),"")</f>
+        <v/>
+      </c>
+      <c r="J13" s="35" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="18" t="inlineStr">
+      <c r="A14" s="36" t="inlineStr">
         <is>
           <t>Congelados</t>
         </is>
       </c>
-      <c r="B14" s="19" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="C14" s="14" t="n"/>
-      <c r="D14" s="14" t="n"/>
-      <c r="E14" s="15">
-        <f>IF(C14=0,"",D14/C14)</f>
-        <v/>
-      </c>
-      <c r="F14" s="16">
-        <f>IF(E14="","",E14-B14)</f>
-        <v/>
-      </c>
-      <c r="G14" s="17">
-        <f>IF(E14="","",IF(E14&lt;=B14,"OK","ALERTA"))</f>
-        <v/>
-      </c>
-      <c r="H14" s="10" t="n"/>
+      <c r="B14" s="37" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="C14" s="31" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="D14" s="37" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="E14" s="32" t="n"/>
+      <c r="F14" s="32" t="n"/>
+      <c r="G14" s="37">
+        <f>IFERROR(IF(E14=0,"",F14/E14),"")</f>
+        <v/>
+      </c>
+      <c r="H14" s="38">
+        <f>IFERROR(IF(G14="","",G14-C14),"")</f>
+        <v/>
+      </c>
+      <c r="I14" s="39">
+        <f>IFERROR(IF(G14="","",IF(G14&lt;=C14,"OK","ALERTA")),"")</f>
+        <v/>
+      </c>
+      <c r="J14" s="35" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="12" t="inlineStr">
+      <c r="A15" s="29" t="inlineStr">
         <is>
           <t>Pan/bollería</t>
         </is>
       </c>
-      <c r="B15" s="13" t="n">
+      <c r="B15" s="30" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="C15" s="31" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="D15" s="30" t="n">
         <v>0.1</v>
       </c>
-      <c r="C15" s="14" t="n"/>
-      <c r="D15" s="14" t="n"/>
-      <c r="E15" s="15">
-        <f>IF(C15=0,"",D15/C15)</f>
-        <v/>
-      </c>
-      <c r="F15" s="16">
-        <f>IF(E15="","",E15-B15)</f>
-        <v/>
-      </c>
-      <c r="G15" s="17">
-        <f>IF(E15="","",IF(E15&lt;=B15,"OK","ALERTA"))</f>
-        <v/>
-      </c>
-      <c r="H15" s="10" t="n"/>
+      <c r="E15" s="32" t="n">
+        <v>310</v>
+      </c>
+      <c r="F15" s="32" t="n">
+        <v>34</v>
+      </c>
+      <c r="G15" s="30">
+        <f>IFERROR(IF(E15=0,"",F15/E15),"")</f>
+        <v>0.10967741935483871</v>
+      </c>
+      <c r="H15" s="33">
+        <f>IFERROR(IF(G15="","",G15-C15),"")</f>
+        <v>0.02967741935483871</v>
+      </c>
+      <c r="I15" s="34" t="str">
+        <f>IFERROR(IF(G15="","",IF(G15&lt;=C15,"OK","ALERTA")),"")</f>
+        <v>ALERTA</v>
+      </c>
+      <c r="J15" s="35" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="18" t="inlineStr">
+      <c r="A16" s="36" t="inlineStr">
         <is>
           <t>Huevos</t>
         </is>
       </c>
-      <c r="B16" s="19" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="C16" s="14" t="n"/>
-      <c r="D16" s="14" t="n"/>
-      <c r="E16" s="15">
-        <f>IF(C16=0,"",D16/C16)</f>
-        <v/>
-      </c>
-      <c r="F16" s="16">
-        <f>IF(E16="","",E16-B16)</f>
-        <v/>
-      </c>
-      <c r="G16" s="17">
-        <f>IF(E16="","",IF(E16&lt;=B16,"OK","ALERTA"))</f>
-        <v/>
-      </c>
-      <c r="H16" s="10" t="n"/>
+      <c r="B16" s="37" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="C16" s="31" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D16" s="37" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="E16" s="32" t="n"/>
+      <c r="F16" s="32" t="n"/>
+      <c r="G16" s="37">
+        <f>IFERROR(IF(E16=0,"",F16/E16),"")</f>
+        <v/>
+      </c>
+      <c r="H16" s="38">
+        <f>IFERROR(IF(G16="","",G16-C16),"")</f>
+        <v/>
+      </c>
+      <c r="I16" s="39">
+        <f>IFERROR(IF(G16="","",IF(G16&lt;=C16,"OK","ALERTA")),"")</f>
+        <v/>
+      </c>
+      <c r="J16" s="35" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="12" t="inlineStr">
+      <c r="A17" s="29" t="inlineStr">
         <is>
           <t>Aceites/grasas</t>
         </is>
       </c>
-      <c r="B17" s="13" t="n">
+      <c r="B17" s="30" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="C17" s="31" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D17" s="30" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="E17" s="32" t="n"/>
+      <c r="F17" s="32" t="n"/>
+      <c r="G17" s="30">
+        <f>IFERROR(IF(E17=0,"",F17/E17),"")</f>
+        <v/>
+      </c>
+      <c r="H17" s="33">
+        <f>IFERROR(IF(G17="","",G17-C17),"")</f>
+        <v/>
+      </c>
+      <c r="I17" s="34">
+        <f>IFERROR(IF(G17="","",IF(G17&lt;=C17,"OK","ALERTA")),"")</f>
+        <v/>
+      </c>
+      <c r="J17" s="35" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="36" t="inlineStr">
+        <is>
+          <t>Especias/hierbas</t>
+        </is>
+      </c>
+      <c r="B18" s="37" t="n">
         <v>0.03</v>
       </c>
-      <c r="C17" s="14" t="n"/>
-      <c r="D17" s="14" t="n"/>
-      <c r="E17" s="15">
-        <f>IF(C17=0,"",D17/C17)</f>
-        <v/>
-      </c>
-      <c r="F17" s="16">
-        <f>IF(E17="","",E17-B17)</f>
-        <v/>
-      </c>
-      <c r="G17" s="17">
-        <f>IF(E17="","",IF(E17&lt;=B17,"OK","ALERTA"))</f>
-        <v/>
-      </c>
-      <c r="H17" s="10" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="18" t="inlineStr">
-        <is>
-          <t>Especias/hierbas</t>
-        </is>
-      </c>
-      <c r="B18" s="19" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="C18" s="14" t="n"/>
-      <c r="D18" s="14" t="n"/>
-      <c r="E18" s="15">
-        <f>IF(C18=0,"",D18/C18)</f>
-        <v/>
-      </c>
-      <c r="F18" s="16">
-        <f>IF(E18="","",E18-B18)</f>
-        <v/>
-      </c>
-      <c r="G18" s="17">
-        <f>IF(E18="","",IF(E18&lt;=B18,"OK","ALERTA"))</f>
-        <v/>
-      </c>
-      <c r="H18" s="10" t="n"/>
+      <c r="C18" s="31" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D18" s="37" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="E18" s="32" t="n"/>
+      <c r="F18" s="32" t="n"/>
+      <c r="G18" s="37">
+        <f>IFERROR(IF(E18=0,"",F18/E18),"")</f>
+        <v/>
+      </c>
+      <c r="H18" s="38">
+        <f>IFERROR(IF(G18="","",G18-C18),"")</f>
+        <v/>
+      </c>
+      <c r="I18" s="39">
+        <f>IFERROR(IF(G18="","",IF(G18&lt;=C18,"OK","ALERTA")),"")</f>
+        <v/>
+      </c>
+      <c r="J18" s="35" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="12" t="inlineStr">
+      <c r="A19" s="29" t="inlineStr">
         <is>
           <t>Chocolate/cacao</t>
         </is>
       </c>
-      <c r="B19" s="13" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="C19" s="14" t="n"/>
-      <c r="D19" s="14" t="n"/>
-      <c r="E19" s="15">
-        <f>IF(C19=0,"",D19/C19)</f>
-        <v/>
-      </c>
-      <c r="F19" s="16">
-        <f>IF(E19="","",E19-B19)</f>
-        <v/>
-      </c>
-      <c r="G19" s="17">
-        <f>IF(E19="","",IF(E19&lt;=B19,"OK","ALERTA"))</f>
-        <v/>
-      </c>
-      <c r="H19" s="10" t="n"/>
+      <c r="B19" s="30" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="C19" s="31" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D19" s="30" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="E19" s="32" t="n"/>
+      <c r="F19" s="32" t="n"/>
+      <c r="G19" s="30">
+        <f>IFERROR(IF(E19=0,"",F19/E19),"")</f>
+        <v/>
+      </c>
+      <c r="H19" s="33">
+        <f>IFERROR(IF(G19="","",G19-C19),"")</f>
+        <v/>
+      </c>
+      <c r="I19" s="34">
+        <f>IFERROR(IF(G19="","",IF(G19&lt;=C19,"OK","ALERTA")),"")</f>
+        <v/>
+      </c>
+      <c r="J19" s="35" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="18" t="inlineStr">
+      <c r="A20" s="36" t="inlineStr">
         <is>
           <t>Bebidas/licores</t>
         </is>
       </c>
-      <c r="B20" s="19" t="n">
+      <c r="B20" s="37" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="C20" s="31" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="D20" s="37" t="n">
         <v>0.02</v>
       </c>
-      <c r="C20" s="14" t="n"/>
-      <c r="D20" s="14" t="n"/>
-      <c r="E20" s="15">
-        <f>IF(C20=0,"",D20/C20)</f>
-        <v/>
-      </c>
-      <c r="F20" s="16">
-        <f>IF(E20="","",E20-B20)</f>
-        <v/>
-      </c>
-      <c r="G20" s="17">
-        <f>IF(E20="","",IF(E20&lt;=B20,"OK","ALERTA"))</f>
-        <v/>
-      </c>
-      <c r="H20" s="10" t="n"/>
+      <c r="E20" s="32" t="n"/>
+      <c r="F20" s="32" t="n"/>
+      <c r="G20" s="37">
+        <f>IFERROR(IF(E20=0,"",F20/E20),"")</f>
+        <v/>
+      </c>
+      <c r="H20" s="38">
+        <f>IFERROR(IF(G20="","",G20-C20),"")</f>
+        <v/>
+      </c>
+      <c r="I20" s="39">
+        <f>IFERROR(IF(G20="","",IF(G20&lt;=C20,"OK","ALERTA")),"")</f>
+        <v/>
+      </c>
+      <c r="J20" s="35" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="20" t="inlineStr">
+      <c r="A21" s="40" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C21" s="21">
-        <f>SUM(C5:C20)</f>
-        <v>0.0</v>
-      </c>
-      <c r="D21" s="21">
-        <f>SUM(D5:D20)</f>
-        <v>0.0</v>
-      </c>
-      <c r="E21" s="22">
-        <f>IF(C21=0,"",D21/C21)</f>
-        <v/>
+      <c r="B21" s="41" t="n"/>
+      <c r="C21" s="40" t="n"/>
+      <c r="D21" s="40" t="n"/>
+      <c r="E21" s="42">
+        <f>SUM(E5:E20)</f>
+        <v>4500.0</v>
+      </c>
+      <c r="F21" s="43">
+        <f>SUM(F5:F20)</f>
+        <v>245.0</v>
+      </c>
+      <c r="G21" s="44">
+        <f>IFERROR(IF(E21=0,"",F21/E21),"")</f>
+        <v>0.05444444444444444</v>
+      </c>
+      <c r="H21" s="41" t="n"/>
+      <c r="I21" s="41" t="n"/>
+      <c r="J21" s="41" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="26" t="n"/>
+      <c r="B22" s="26" t="n"/>
+      <c r="C22" s="26" t="n"/>
+      <c r="D22" s="26" t="n"/>
+      <c r="E22" s="26" t="n"/>
+      <c r="F22" s="26" t="n"/>
+      <c r="G22" s="26" t="n"/>
+      <c r="H22" s="26" t="n"/>
+      <c r="I22" s="26" t="n"/>
+      <c r="J22" s="26" t="n"/>
+    </row>
+    <row r="23" ht="26" customHeight="1">
+      <c r="A23" s="45" t="inlineStr">
+        <is>
+          <t>Aquí se registra el DESPERDICIO (caducidad, mal estado, sobreproducción, porcionado): euros tirados sobre euros comprados. La merma de despiece y limpieza NO va aquí — ya está cobrada dentro del coste del plato, en las plantillas de escandallo (hoja «Mermas»). Mezclarlas era el error de la v1.1: con un objetivo del 45 % un marisco podrido daba «OK».</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="26" customHeight="1">
+      <c r="A24" s="45" t="inlineStr">
+        <is>
+          <t>Objetivos de referencia sobre la compra: secos y congelados 2-3 % · carne y pescado 3-5 % · verdura y fruta 5-8 % · bebidas 1-2 % · pan y bollería 5-10 % (sobreproducción). El «objetivo típico» es la celda verde: ajústalo a tu casa; mínimo y máximo son la horquilla del sector.</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:H1"/>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
+  <mergeCells count="3">
+    <mergeCell ref="A23:J23"/>
+    <mergeCell ref="A24:J24"/>
+    <mergeCell ref="A1:J1"/>
   </mergeCells>
+  <conditionalFormatting sqref="I5:I20">
+    <cfRule type="cellIs" priority="1" operator="equal" dxfId="0" stopIfTrue="0">
+      <formula>"ALERTA"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="2" operator="equal" dxfId="1" stopIfTrue="0">
+      <formula>"OK"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G5:G20">
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00C6EFCE"/>
+        <color rgb="00FFEB9C"/>
+        <color rgb="00FFC7CE"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
@@ -1197,4 +1820,335 @@
     <firstFooter/>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:E18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="23" t="inlineStr">
+        <is>
+          <t>Evolución del desperdicio — 12 semanas</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="69" customHeight="1">
+      <c r="A2" s="46" t="inlineStr">
+        <is>
+          <t>La fila «Semana en curso» está ENLAZADA a «Mermas Semanal»: cambia sola según rellenas la semana. Cada lunes, ANTES de vaciar el registro semanal, copia su total (compra y desperdicio) en la fila de la semana que cierras y pega VALORES, no fórmulas — empezando por la Semana 1, cuyo enlace se sustituye al pegar encima. Si no lo haces, la semana 1 seguirá enseñando lo que haya en la hoja semanal y perderás el histórico, que es justo lo que esta pestaña existe para guardar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="24" t="inlineStr">
+        <is>
+          <t>Objetivo global de desperdicio (%)</t>
+        </is>
+      </c>
+      <c r="B3" s="47" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="C3" s="26" t="n"/>
+      <c r="D3" s="26" t="n"/>
+      <c r="E3" s="26" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="26" t="n"/>
+      <c r="B4" s="26" t="n"/>
+      <c r="C4" s="26" t="n"/>
+      <c r="D4" s="26" t="n"/>
+      <c r="E4" s="26" t="n"/>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="28" t="inlineStr">
+        <is>
+          <t>Semana</t>
+        </is>
+      </c>
+      <c r="B5" s="28" t="inlineStr">
+        <is>
+          <t>Compra total (€)</t>
+        </is>
+      </c>
+      <c r="C5" s="28" t="inlineStr">
+        <is>
+          <t>Desperdicio (€)</t>
+        </is>
+      </c>
+      <c r="D5" s="28" t="inlineStr">
+        <is>
+          <t>Desperdicio (%)</t>
+        </is>
+      </c>
+      <c r="E5" s="28" t="inlineStr">
+        <is>
+          <t>Objetivo (%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="48" t="inlineStr">
+        <is>
+          <t>Semana en curso (enlazada a «Mermas Semanal» — pega encima el valor al cerrarla)</t>
+        </is>
+      </c>
+      <c r="B6" s="49">
+        <f>'Mermas Semanal'!E21</f>
+        <v>4500.0</v>
+      </c>
+      <c r="C6" s="49">
+        <f>'Mermas Semanal'!F21</f>
+        <v>245.0</v>
+      </c>
+      <c r="D6" s="50">
+        <f>IF(B6=0,NA(),C6/B6)</f>
+        <v>0.05444444444444444</v>
+      </c>
+      <c r="E6" s="50">
+        <f>IF(B6=0,NA(),$B$3)</f>
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="51" t="inlineStr">
+        <is>
+          <t>Semana 2</t>
+        </is>
+      </c>
+      <c r="B7" s="52" t="n">
+        <v>4300</v>
+      </c>
+      <c r="C7" s="52" t="n">
+        <v>205</v>
+      </c>
+      <c r="D7" s="53">
+        <f>IF(B7=0,NA(),C7/B7)</f>
+        <v>0.047674418604651166</v>
+      </c>
+      <c r="E7" s="53">
+        <f>IF(B7=0,NA(),$B$3)</f>
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="48" t="inlineStr">
+        <is>
+          <t>Semana 3</t>
+        </is>
+      </c>
+      <c r="B8" s="52" t="n">
+        <v>4150</v>
+      </c>
+      <c r="C8" s="52" t="n">
+        <v>168</v>
+      </c>
+      <c r="D8" s="50">
+        <f>IF(B8=0,NA(),C8/B8)</f>
+        <v>0.04048192771084337</v>
+      </c>
+      <c r="E8" s="50">
+        <f>IF(B8=0,NA(),$B$3)</f>
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="51" t="inlineStr">
+        <is>
+          <t>Semana 4</t>
+        </is>
+      </c>
+      <c r="B9" s="52" t="n">
+        <v>4400</v>
+      </c>
+      <c r="C9" s="52" t="n">
+        <v>154</v>
+      </c>
+      <c r="D9" s="53">
+        <f>IF(B9=0,NA(),C9/B9)</f>
+        <v>0.035</v>
+      </c>
+      <c r="E9" s="53">
+        <f>IF(B9=0,NA(),$B$3)</f>
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="48" t="inlineStr">
+        <is>
+          <t>Semana 5</t>
+        </is>
+      </c>
+      <c r="B10" s="52" t="n"/>
+      <c r="C10" s="52" t="n"/>
+      <c r="D10" s="50" t="str">
+        <f>IF(B10=0,NA(),C10/B10)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E10" s="50" t="str">
+        <f>IF(B10=0,NA(),$B$3)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="51" t="inlineStr">
+        <is>
+          <t>Semana 6</t>
+        </is>
+      </c>
+      <c r="B11" s="52" t="n"/>
+      <c r="C11" s="52" t="n"/>
+      <c r="D11" s="53" t="str">
+        <f>IF(B11=0,NA(),C11/B11)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E11" s="53" t="str">
+        <f>IF(B11=0,NA(),$B$3)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="48" t="inlineStr">
+        <is>
+          <t>Semana 7</t>
+        </is>
+      </c>
+      <c r="B12" s="52" t="n"/>
+      <c r="C12" s="52" t="n"/>
+      <c r="D12" s="50" t="str">
+        <f>IF(B12=0,NA(),C12/B12)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E12" s="50" t="str">
+        <f>IF(B12=0,NA(),$B$3)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="51" t="inlineStr">
+        <is>
+          <t>Semana 8</t>
+        </is>
+      </c>
+      <c r="B13" s="52" t="n"/>
+      <c r="C13" s="52" t="n"/>
+      <c r="D13" s="53" t="str">
+        <f>IF(B13=0,NA(),C13/B13)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E13" s="53" t="str">
+        <f>IF(B13=0,NA(),$B$3)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="48" t="inlineStr">
+        <is>
+          <t>Semana 9</t>
+        </is>
+      </c>
+      <c r="B14" s="52" t="n"/>
+      <c r="C14" s="52" t="n"/>
+      <c r="D14" s="50" t="str">
+        <f>IF(B14=0,NA(),C14/B14)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E14" s="50" t="str">
+        <f>IF(B14=0,NA(),$B$3)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="51" t="inlineStr">
+        <is>
+          <t>Semana 10</t>
+        </is>
+      </c>
+      <c r="B15" s="52" t="n"/>
+      <c r="C15" s="52" t="n"/>
+      <c r="D15" s="53" t="str">
+        <f>IF(B15=0,NA(),C15/B15)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E15" s="53" t="str">
+        <f>IF(B15=0,NA(),$B$3)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="48" t="inlineStr">
+        <is>
+          <t>Semana 11</t>
+        </is>
+      </c>
+      <c r="B16" s="52" t="n"/>
+      <c r="C16" s="52" t="n"/>
+      <c r="D16" s="50" t="str">
+        <f>IF(B16=0,NA(),C16/B16)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E16" s="50" t="str">
+        <f>IF(B16=0,NA(),$B$3)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="51" t="inlineStr">
+        <is>
+          <t>Semana 12</t>
+        </is>
+      </c>
+      <c r="B17" s="52" t="n"/>
+      <c r="C17" s="52" t="n"/>
+      <c r="D17" s="53" t="str">
+        <f>IF(B17=0,NA(),C17/B17)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E17" s="53" t="str">
+        <f>IF(B17=0,NA(),$B$3)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="26" t="n"/>
+      <c r="B18" s="26" t="n"/>
+      <c r="C18" s="26" t="n"/>
+      <c r="D18" s="26" t="n"/>
+      <c r="E18" s="26" t="n"/>
+    </row>
+  </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A2:E2"/>
+  </mergeCells>
+  <conditionalFormatting sqref="D6:E17">
+    <cfRule type="expression" priority="1" dxfId="2" stopIfTrue="1">
+      <formula>ISNA(D6)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
 </file>